--- a/data/trans_camb/P7_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P7_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 3,43</t>
+          <t>-4,96; 3,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 0,21</t>
+          <t>-7,74; 0,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 6,39</t>
+          <t>-2,88; 6,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,24; -0,95</t>
+          <t>-11,94; -1,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,53; -1,76</t>
+          <t>-11,65; -0,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 2,17</t>
+          <t>-8,21; 1,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 0,06</t>
+          <t>-6,67; 0,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,14; -1,78</t>
+          <t>-8,36; -1,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 3,18</t>
+          <t>-3,02; 3,38</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-39,81; 36,99</t>
+          <t>-37,28; 41,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-55,6; 4,82</t>
+          <t>-55,5; 3,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-19,85; 67,73</t>
+          <t>-19,77; 64,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-62,19; -5,96</t>
+          <t>-60,89; -7,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-62,45; -10,96</t>
+          <t>-60,39; -5,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-38,34; 17,09</t>
+          <t>-41,19; 14,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-43,72; 0,48</t>
+          <t>-43,54; 2,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-53,81; -14,95</t>
+          <t>-53,23; -14,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-20,35; 27,35</t>
+          <t>-20,4; 30,72</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 4,46</t>
+          <t>-4,36; 4,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 5,76</t>
+          <t>-3,96; 5,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 5,84</t>
+          <t>-2,82; 5,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 3,86</t>
+          <t>-6,86; 4,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 3,53</t>
+          <t>-6,8; 3,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 3,92</t>
+          <t>-5,79; 3,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 3,15</t>
+          <t>-4,07; 2,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 2,67</t>
+          <t>-4,12; 2,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 3,09</t>
+          <t>-3,27; 3,44</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-39,33; 52,11</t>
+          <t>-34,67; 60,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-27,97; 71,02</t>
+          <t>-32,04; 62,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-22,12; 69,45</t>
+          <t>-22,06; 72,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-38,74; 30,25</t>
+          <t>-38,51; 34,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-38,75; 28,39</t>
+          <t>-38,9; 33,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-29,71; 32,52</t>
+          <t>-32,89; 30,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-28,87; 28,22</t>
+          <t>-27,82; 23,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-29,18; 23,56</t>
+          <t>-27,96; 22,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-20,17; 28,39</t>
+          <t>-21,78; 30,63</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,16; 10,59</t>
+          <t>1,18; 10,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 5,74</t>
+          <t>-3,56; 5,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,65; 6,51</t>
+          <t>-13,14; 6,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,62; 3,73</t>
+          <t>-12,26; 4,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,8; 9,48</t>
+          <t>-11,55; 9,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 8,85</t>
+          <t>-8,22; 9,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 7,83</t>
+          <t>-0,49; 8,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 5,16</t>
+          <t>-3,17; 5,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-13,25; 5,63</t>
+          <t>-12,95; 5,51</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,34; 74,91</t>
+          <t>5,47; 77,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-20,28; 39,37</t>
+          <t>-19,07; 41,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-69,79; 41,77</t>
+          <t>-68,7; 42,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-41,0; 16,7</t>
+          <t>-38,3; 22,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-32,46; 39,95</t>
+          <t>-35,53; 41,79</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-25,83; 37,87</t>
+          <t>-25,76; 41,24</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 48,37</t>
+          <t>-2,19; 46,89</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-17,25; 29,33</t>
+          <t>-15,03; 29,17</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-66,71; 30,74</t>
+          <t>-60,73; 29,74</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 4,4</t>
+          <t>-2,62; 4,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 3,45</t>
+          <t>-3,07; 3,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 6,58</t>
+          <t>-0,41; 6,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 1,43</t>
+          <t>-7,14; 1,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,87; -0,08</t>
+          <t>-8,83; -0,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-17,31; -2,14</t>
+          <t>-16,83; -2,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 2,05</t>
+          <t>-3,0; 2,2</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 1,04</t>
+          <t>-3,98; 1,0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 1,51</t>
+          <t>-7,86; 1,57</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-11,33; 25,42</t>
+          <t>-12,65; 22,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-14,08; 19,78</t>
+          <t>-14,68; 19,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 37,46</t>
+          <t>-2,12; 36,07</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,14; 6,97</t>
+          <t>-27,1; 6,74</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-33,3; -0,2</t>
+          <t>-32,89; -1,55</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-67,62; -9,61</t>
+          <t>-61,62; -8,95</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-14,24; 10,16</t>
+          <t>-13,58; 10,99</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-18,81; 5,36</t>
+          <t>-17,57; 5,18</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-32,32; 7,16</t>
+          <t>-37,59; 7,56</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,3; 0,45</t>
+          <t>-9,94; 1,33</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 3,85</t>
+          <t>-7,23; 4,23</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 6,5</t>
+          <t>-6,46; 6,1</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 8,8</t>
+          <t>-2,45; 8,43</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 3,49</t>
+          <t>-6,99; 3,81</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,73; 3,38</t>
+          <t>-11,64; 3,61</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 4,01</t>
+          <t>-3,78; 3,72</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 1,8</t>
+          <t>-5,73; 1,89</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 2,94</t>
+          <t>-7,43; 2,57</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-38,98; 2,67</t>
+          <t>-37,85; 7,48</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-28,43; 19,67</t>
+          <t>-26,6; 22,36</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-23,06; 35,92</t>
+          <t>-24,05; 31,5</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 29,03</t>
+          <t>-7,31; 27,74</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-19,5; 11,67</t>
+          <t>-19,56; 12,52</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-33,14; 10,59</t>
+          <t>-31,73; 11,81</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-12,53; 15,06</t>
+          <t>-12,48; 14,32</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-18,98; 6,19</t>
+          <t>-18,24; 7,71</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-22,73; 10,53</t>
+          <t>-24,49; 9,15</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 4,88</t>
+          <t>-2,44; 5,28</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 2,13</t>
+          <t>-3,8; 2,17</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 1,92</t>
+          <t>-3,83; 2,14</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 0,34</t>
+          <t>-7,27; 0,72</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-11,1; -2,95</t>
+          <t>-11,05; -3,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-9,62; -1,77</t>
+          <t>-10,01; -1,81</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 1,3</t>
+          <t>-5,75; 0,82</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-9,58; -3,06</t>
+          <t>-9,47; -2,9</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-9,4; -2,95</t>
+          <t>-9,26; -2,43</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-48,1; 198,71</t>
+          <t>-47,03; 231,04</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-68,17; 107,14</t>
+          <t>-68,5; 104,77</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-70,28; 75,75</t>
+          <t>-67,66; 104,66</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-19,77; 1,18</t>
+          <t>-19,26; 2,11</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-29,65; -8,7</t>
+          <t>-29,27; -8,51</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-25,54; -5,32</t>
+          <t>-26,33; -5,34</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-18,04; 4,62</t>
+          <t>-18,28; 2,96</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-31,05; -10,57</t>
+          <t>-30,29; -10,22</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-30,1; -10,26</t>
+          <t>-30,29; -9,07</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 2,99</t>
+          <t>-0,66; 2,99</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 1,98</t>
+          <t>-1,66; 1,97</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 3,25</t>
+          <t>-2,81; 3,17</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 0,36</t>
+          <t>-4,3; 0,22</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,84; -2,5</t>
+          <t>-7,08; -2,46</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-10,45; -3,57</t>
+          <t>-10,11; -3,39</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 0,99</t>
+          <t>-1,85; 0,97</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,74; -0,92</t>
+          <t>-3,73; -0,98</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-5,36; -0,77</t>
+          <t>-5,15; -0,83</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 20,44</t>
+          <t>-4,08; 20,2</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-10,24; 13,54</t>
+          <t>-9,8; 13,37</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-15,86; 21,68</t>
+          <t>-16,75; 20,89</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-13,52; 1,25</t>
+          <t>-14,42; 0,82</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-23,01; -8,97</t>
+          <t>-23,6; -9,09</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-36,29; -12,72</t>
+          <t>-35,45; -12,33</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 4,56</t>
+          <t>-8,12; 4,48</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-16,42; -4,56</t>
+          <t>-16,15; -4,58</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-23,53; -3,6</t>
+          <t>-22,77; -3,85</t>
         </is>
       </c>
     </row>
